--- a/data/trans_dic/P22$mutuaSPriv-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutuaSPriv-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Privado)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (seguro privado) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,81</t>
+          <t>0,17; 1,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,74</t>
+          <t>0,82; 3,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,84</t>
+          <t>0,99; 4,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,44</t>
+          <t>0,9; 7,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,55</t>
+          <t>1,02; 3,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,53</t>
+          <t>0,72; 7,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,06</t>
+          <t>0,73; 2,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,29</t>
+          <t>0,57; 2,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,52</t>
+          <t>0,87; 2,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,45</t>
+          <t>1,3; 5,57</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,85</t>
+          <t>1,92; 4,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,11</t>
+          <t>1,49; 4,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,04</t>
+          <t>0,84; 3,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,68</t>
+          <t>0,39; 3,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,87</t>
+          <t>1,16; 3,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,14</t>
+          <t>0,8; 3,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,21</t>
+          <t>1,03; 3,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,06</t>
+          <t>1,49; 5,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,66</t>
+          <t>1,86; 3,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,03</t>
+          <t>1,4; 3,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,63</t>
+          <t>1,22; 2,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,74</t>
+          <t>1,33; 3,66</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,51</t>
+          <t>1,16; 3,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,7</t>
+          <t>1,88; 4,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,8</t>
+          <t>1,18; 3,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,68</t>
+          <t>0,99; 3,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,24</t>
+          <t>0,57; 2,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,67</t>
+          <t>1,8; 4,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,75</t>
+          <t>1,3; 3,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,93</t>
+          <t>1,66; 3,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,52</t>
+          <t>1,07; 2,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,23</t>
+          <t>2,08; 4,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,17</t>
+          <t>1,45; 3,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,32</t>
+          <t>1,58; 3,39</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,92</t>
+          <t>1,22; 4,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,74</t>
+          <t>0,88; 3,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,66</t>
+          <t>1,63; 4,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,57</t>
+          <t>1,1; 4,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,0</t>
+          <t>1,67; 5,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,15</t>
+          <t>1,61; 5,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,28</t>
+          <t>1,11; 3,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,94</t>
+          <t>1,94; 3,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,02</t>
+          <t>1,74; 3,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,83</t>
+          <t>1,58; 3,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,47</t>
+          <t>1,61; 3,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,72</t>
+          <t>1,6; 3,76</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,86</t>
+          <t>1,21; 4,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,86</t>
+          <t>0,73; 3,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,74</t>
+          <t>0,9; 3,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,65</t>
+          <t>1,97; 4,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,23</t>
+          <t>1,58; 5,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,79</t>
+          <t>0,46; 2,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,83</t>
+          <t>0,84; 4,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,84</t>
+          <t>1,81; 3,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,14</t>
+          <t>1,76; 4,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,7</t>
+          <t>0,77; 2,74</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,12</t>
+          <t>1,14; 3,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,94</t>
+          <t>2,15; 3,84</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,44</t>
+          <t>0,96; 4,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,82</t>
+          <t>1,0; 6,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,22</t>
+          <t>0,28; 2,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,18</t>
+          <t>2,52; 5,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,15</t>
+          <t>1,07; 4,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,76</t>
+          <t>0,27; 2,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,58</t>
+          <t>0,55; 3,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,27</t>
+          <t>0,69; 3,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,62</t>
+          <t>1,31; 3,59</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,5</t>
+          <t>0,86; 3,72</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,7</t>
+          <t>0,65; 2,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,78</t>
+          <t>1,28; 3,91</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,33</t>
+          <t>0,36; 3,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,78</t>
+          <t>0,62; 4,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,58</t>
+          <t>1,53; 4,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,29</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,04</t>
+          <t>0,5; 4,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,23</t>
+          <t>0,58; 2,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,32</t>
+          <t>0,4; 2,3</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,63</t>
+          <t>0,48; 2,61</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,12</t>
+          <t>0,51; 2,22</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,76</t>
+          <t>1,14; 2,8</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,7</t>
+          <t>1,67; 2,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,8</t>
+          <t>1,68; 2,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,71</t>
+          <t>1,58; 2,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,4</t>
+          <t>1,99; 3,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,61</t>
+          <t>1,59; 2,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,46</t>
+          <t>1,43; 2,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,2</t>
+          <t>1,29; 2,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,86; 2,97</t>
+          <t>1,9; 2,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,49</t>
+          <t>1,74; 2,45</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,47</t>
+          <t>1,69; 2,42</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,25</t>
+          <t>1,55; 2,22</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,14; 2,98</t>
+          <t>2,12; 3,02</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Privado)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (seguro privado) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>994; 8928</t>
+          <t>846; 8219</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3841; 16965</t>
+          <t>3701; 16339</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4282; 16022</t>
+          <t>4138; 17126</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3358; 29775</t>
+          <t>3581; 30763</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4033; 16606</t>
+          <t>4766; 16338</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7026</t>
+          <t>0; 6046</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>946; 8679</t>
+          <t>947; 8687</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2194; 20447</t>
+          <t>2245; 22008</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6547; 19833</t>
+          <t>7035; 21859</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5850; 20214</t>
+          <t>4997; 19951</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6240; 20510</t>
+          <t>7047; 20343</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8550; 38881</t>
+          <t>9270; 39714</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14590; 35530</t>
+          <t>14093; 33715</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10256; 28273</t>
+          <t>10219; 27782</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4897; 17930</t>
+          <t>4938; 18170</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1613; 15602</t>
+          <t>1640; 15403</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7827; 24180</t>
+          <t>7269; 22404</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4932; 19148</t>
+          <t>4867; 18283</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4952; 18052</t>
+          <t>5790; 17762</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7649; 25876</t>
+          <t>7633; 25913</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24404; 49704</t>
+          <t>25329; 51722</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18640; 39289</t>
+          <t>18118; 39637</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13431; 30319</t>
+          <t>14094; 31564</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12715; 35001</t>
+          <t>12394; 34259</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7372; 22402</t>
+          <t>7391; 22213</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12687; 32077</t>
+          <t>12843; 32084</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7749; 25390</t>
+          <t>7893; 25009</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5245; 19733</t>
+          <t>5285; 19239</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3786; 15482</t>
+          <t>3923; 15401</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13258; 33176</t>
+          <t>12779; 32177</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8615; 24835</t>
+          <t>8584; 24189</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9041; 21306</t>
+          <t>9029; 20792</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14098; 33463</t>
+          <t>14268; 33063</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30619; 58888</t>
+          <t>28983; 56203</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19390; 42190</t>
+          <t>19326; 42096</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16939; 35779</t>
+          <t>17095; 36614</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6623; 20323</t>
+          <t>6325; 20814</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5713; 22999</t>
+          <t>5398; 24160</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11057; 30103</t>
+          <t>10507; 30762</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9295; 40538</t>
+          <t>9734; 38953</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9169; 25712</t>
+          <t>8593; 26392</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10647; 31754</t>
+          <t>9925; 31247</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6513; 21290</t>
+          <t>7226; 21064</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13859; 28074</t>
+          <t>13847; 27386</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18086; 41502</t>
+          <t>17935; 38980</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20355; 47081</t>
+          <t>19424; 46592</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19998; 44916</t>
+          <t>20892; 45654</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25557; 59558</t>
+          <t>25685; 60229</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4618; 18813</t>
+          <t>4663; 18576</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3131; 16592</t>
+          <t>3137; 16834</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4665; 17799</t>
+          <t>4302; 16435</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10506; 26110</t>
+          <t>11080; 27381</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6727; 21074</t>
+          <t>6362; 21220</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2023; 12476</t>
+          <t>2057; 11679</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3528; 19039</t>
+          <t>4197; 20732</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9807; 20959</t>
+          <t>9869; 21328</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14229; 32706</t>
+          <t>13933; 33753</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6556; 23649</t>
+          <t>6729; 24024</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11247; 30388</t>
+          <t>11090; 30282</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23153; 43567</t>
+          <t>23842; 42482</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2761; 12986</t>
+          <t>2804; 12929</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2242; 18025</t>
+          <t>3112; 18607</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>933; 10775</t>
+          <t>937; 9613</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9869; 22739</t>
+          <t>9268; 21712</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3255; 14245</t>
+          <t>3663; 14159</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1047; 9755</t>
+          <t>963; 9788</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2038; 13446</t>
+          <t>2077; 14229</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3640; 19897</t>
+          <t>4186; 19716</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8512; 23007</t>
+          <t>8298; 22843</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5180; 23209</t>
+          <t>5692; 24686</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4973; 19179</t>
+          <t>4607; 18090</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12515; 36877</t>
+          <t>12530; 38220</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>747; 6918</t>
+          <t>757; 6902</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6087</t>
+          <t>0; 7031</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1557; 9721</t>
+          <t>1593; 10332</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4055; 12938</t>
+          <t>4325; 12831</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>920; 7646</t>
+          <t>0; 8400</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2138; 15718</t>
+          <t>1936; 15900</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 8790</t>
+          <t>0; 7731</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2361; 9475</t>
+          <t>2459; 10341</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2437; 12573</t>
+          <t>2172; 12441</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3044; 16778</t>
+          <t>3039; 16692</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3142; 13908</t>
+          <t>3375; 14540</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8230; 19526</t>
+          <t>8050; 19858</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>54170; 88277</t>
+          <t>54737; 89218</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>58359; 95847</t>
+          <t>57480; 96884</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>55232; 91957</t>
+          <t>53673; 88165</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>71187; 117591</t>
+          <t>68990; 117270</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>54954; 88275</t>
+          <t>53667; 87804</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>51711; 87500</t>
+          <t>50914; 89206</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>46180; 77953</t>
+          <t>45600; 76957</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>68222; 108676</t>
+          <t>69581; 108980</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>117526; 165710</t>
+          <t>115980; 162688</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>117704; 172459</t>
+          <t>118191; 168854</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>106568; 155579</t>
+          <t>107698; 153993</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>152145; 211974</t>
+          <t>150819; 215218</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$mutuaSPriv-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutuaSPriv-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,67</t>
+          <t>0,17; 1,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,61</t>
+          <t>0,85; 3,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,1</t>
+          <t>0,97; 3,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,69</t>
+          <t>1,59; 9,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,49</t>
+          <t>0,84; 3,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,19</t>
+          <t>0,24; 2,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 7,03</t>
+          <t>0,5; 4,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,28</t>
+          <t>0,66; 2,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,26</t>
+          <t>0,6; 2,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,5</t>
+          <t>0,84; 2,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,57</t>
+          <t>1,52; 6,13</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,6</t>
+          <t>1,97; 4,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,04</t>
+          <t>1,58; 3,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,08</t>
+          <t>0,84; 3,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,64</t>
+          <t>0,38; 3,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,58</t>
+          <t>1,22; 3,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,0</t>
+          <t>0,8; 3,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,16</t>
+          <t>1,01; 3,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,07</t>
+          <t>1,76; 5,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,81</t>
+          <t>1,8; 3,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,06</t>
+          <t>1,38; 3,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,74</t>
+          <t>1,16; 2,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,66</t>
+          <t>1,38; 3,7</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,48</t>
+          <t>1,23; 3,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,71</t>
+          <t>1,82; 4,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,74</t>
+          <t>1,09; 3,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,59</t>
+          <t>0,94; 3,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,23</t>
+          <t>0,61; 2,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,53</t>
+          <t>1,87; 4,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,66</t>
+          <t>1,23; 3,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,83</t>
+          <t>1,71; 3,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,49</t>
+          <t>1,06; 2,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,04</t>
+          <t>2,22; 4,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,17</t>
+          <t>1,42; 3,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,39</t>
+          <t>1,58; 3,19</t>
         </is>
       </c>
     </row>
@@ -1084,34 +1084,34 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>2,48%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,02</t>
+          <t>1,13; 3,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,93</t>
+          <t>0,86; 3,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,76</t>
+          <t>1,74; 4,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,39</t>
+          <t>2,24; 5,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,13</t>
+          <t>1,75; 4,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,07</t>
+          <t>1,68; 5,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,25</t>
+          <t>0,99; 3,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,84</t>
+          <t>2,0; 3,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,78</t>
+          <t>1,73; 3,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,79</t>
+          <t>1,57; 3,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,53</t>
+          <t>1,62; 3,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,76</t>
+          <t>2,38; 4,22</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,8</t>
+          <t>1,26; 4,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,92</t>
+          <t>0,72; 4,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,45</t>
+          <t>0,9; 3,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,88</t>
+          <t>1,91; 4,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,26</t>
+          <t>1,7; 5,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,61</t>
+          <t>0,45; 2,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,17</t>
+          <t>0,83; 3,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,91</t>
+          <t>1,75; 3,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,27</t>
+          <t>1,74; 4,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,74</t>
+          <t>0,73; 2,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,11</t>
+          <t>1,24; 3,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,84</t>
+          <t>2,06; 3,76</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,42</t>
+          <t>0,96; 4,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,01</t>
+          <t>0,92; 5,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,88</t>
+          <t>0,28; 2,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,9</t>
+          <t>2,62; 6,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,13</t>
+          <t>1,08; 4,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,76</t>
+          <t>0,28; 2,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,78</t>
+          <t>0,54; 3,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,24</t>
+          <t>1,72; 4,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,59</t>
+          <t>1,21; 3,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,72</t>
+          <t>0,88; 3,42</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,55</t>
+          <t>0,64; 2,45</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,91</t>
+          <t>2,52; 4,51</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,32</t>
+          <t>0,36; 3,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,02</t>
+          <t>0,61; 3,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,54</t>
+          <t>1,48; 4,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,27; 2,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,09</t>
+          <t>0,5; 4,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,43</t>
+          <t>0,58; 2,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,3</t>
+          <t>0,47; 2,15</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,61</t>
+          <t>0,47; 2,83</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,22</t>
+          <t>0,5; 2,21</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,8</t>
+          <t>1,17; 2,75</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,73</t>
+          <t>1,68; 2,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,83</t>
+          <t>1,71; 2,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,6</t>
+          <t>1,58; 2,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,39</t>
+          <t>2,33; 3,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,6</t>
+          <t>1,69; 2,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,51</t>
+          <t>1,44; 2,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,17</t>
+          <t>1,28; 2,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,98</t>
+          <t>2,13; 3,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,45</t>
+          <t>1,78; 2,5</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,42</t>
+          <t>1,72; 2,43</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,22</t>
+          <t>1,52; 2,22</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,02</t>
+          <t>2,35; 3,17</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>16357</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>23990</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>846; 8219</t>
+          <t>849; 8627</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3701; 16339</t>
+          <t>3855; 17725</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4138; 17126</t>
+          <t>4061; 15939</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3581; 30763</t>
+          <t>6478; 37153</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4766; 16338</t>
+          <t>3915; 16811</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6046</t>
+          <t>0; 6702</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>947; 8687</t>
+          <t>949; 9089</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2245; 22008</t>
+          <t>1822; 18075</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7035; 21859</t>
+          <t>6300; 19879</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4997; 19951</t>
+          <t>5315; 18618</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7047; 20343</t>
+          <t>6813; 21518</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9270; 39714</t>
+          <t>11709; 47249</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15421</t>
+          <t>16336</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21740</t>
+          <t>23054</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14093; 33715</t>
+          <t>14425; 33594</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10219; 27782</t>
+          <t>10840; 27204</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4938; 18170</t>
+          <t>4955; 17722</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1640; 15403</t>
+          <t>1822; 17535</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7269; 22404</t>
+          <t>7631; 22854</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4867; 18283</t>
+          <t>4882; 19306</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5790; 17762</t>
+          <t>5660; 18452</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7633; 25913</t>
+          <t>8811; 26693</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25329; 51722</t>
+          <t>24478; 49751</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18118; 39637</t>
+          <t>17890; 39136</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14094; 31564</t>
+          <t>13314; 30606</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12394; 34259</t>
+          <t>13447; 36128</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14054</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24704</t>
+          <t>28012</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7391; 22213</t>
+          <t>7825; 22858</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12843; 32084</t>
+          <t>12421; 32100</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7893; 25009</t>
+          <t>7274; 24404</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5285; 19239</t>
+          <t>5840; 21125</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3923; 15401</t>
+          <t>4226; 15285</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12779; 32177</t>
+          <t>13276; 33581</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8584; 24189</t>
+          <t>8160; 23864</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9029; 20792</t>
+          <t>10660; 23384</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14268; 33063</t>
+          <t>14025; 32696</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28983; 56203</t>
+          <t>30849; 57670</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19326; 42096</t>
+          <t>18830; 42789</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17095; 36614</t>
+          <t>19616; 39688</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23275</t>
+          <t>24779</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19912</t>
+          <t>20862</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>43186</t>
+          <t>45641</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6325; 20814</t>
+          <t>5859; 19732</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5398; 24160</t>
+          <t>5298; 21632</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10507; 30762</t>
+          <t>11215; 30691</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9734; 38953</t>
+          <t>15664; 37933</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8593; 26392</t>
+          <t>8989; 24542</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9925; 31247</t>
+          <t>10344; 32627</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7226; 21064</t>
+          <t>6421; 20355</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13847; 27386</t>
+          <t>14744; 28490</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17935; 38980</t>
+          <t>17875; 39087</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19424; 46592</t>
+          <t>19329; 45124</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20892; 45654</t>
+          <t>20929; 46220</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25685; 60229</t>
+          <t>34246; 60630</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17474</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32012</t>
+          <t>34341</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4663; 18576</t>
+          <t>4883; 17377</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3137; 16834</t>
+          <t>3098; 17373</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4302; 16435</t>
+          <t>4295; 17027</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11080; 27381</t>
+          <t>11635; 27339</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6362; 21220</t>
+          <t>6870; 21877</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2057; 11679</t>
+          <t>2028; 10969</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4197; 20732</t>
+          <t>4147; 19499</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9869; 21328</t>
+          <t>10656; 23454</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13933; 33753</t>
+          <t>13764; 33773</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6729; 24024</t>
+          <t>6417; 22624</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11090; 30282</t>
+          <t>12031; 30819</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23842; 42482</t>
+          <t>25077; 45732</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>11987</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26380</t>
+          <t>28425</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2804; 12929</t>
+          <t>2810; 13418</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3112; 18607</t>
+          <t>2840; 18370</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>937; 9613</t>
+          <t>921; 9929</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9268; 21712</t>
+          <t>10656; 25353</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3663; 14159</t>
+          <t>3697; 14660</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>963; 9788</t>
+          <t>976; 9686</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2077; 14229</t>
+          <t>2046; 12039</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4186; 19716</t>
+          <t>7575; 17621</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8298; 22843</t>
+          <t>7667; 21982</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5692; 24686</t>
+          <t>5811; 22708</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4607; 18090</t>
+          <t>4557; 17436</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12530; 38220</t>
+          <t>21284; 38179</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>14009</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>757; 6902</t>
+          <t>745; 7003</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 7031</t>
+          <t>0; 7043</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1593; 10332</t>
+          <t>1579; 9573</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4325; 12831</t>
+          <t>4588; 14391</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 8400</t>
+          <t>916; 8203</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1936; 15900</t>
+          <t>1962; 17708</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 7731</t>
+          <t>0; 9044</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2459; 10341</t>
+          <t>2706; 11059</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2172; 12441</t>
+          <t>2524; 11669</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3039; 16692</t>
+          <t>2972; 18065</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3375; 14540</t>
+          <t>3254; 14476</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8050; 19858</t>
+          <t>9058; 21292</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>92937</t>
+          <t>103212</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>88283</t>
+          <t>94261</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>181220</t>
+          <t>197473</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>54737; 89218</t>
+          <t>55000; 88610</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>57480; 96884</t>
+          <t>58453; 97014</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>53673; 88165</t>
+          <t>53681; 88495</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>68990; 117270</t>
+          <t>82163; 130113</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>53667; 87804</t>
+          <t>57167; 90229</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>50914; 89206</t>
+          <t>51335; 87605</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>45600; 76957</t>
+          <t>45226; 76426</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>69581; 108980</t>
+          <t>79386; 113514</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>115980; 162688</t>
+          <t>118130; 166093</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>118191; 168854</t>
+          <t>120082; 169987</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>107698; 153993</t>
+          <t>105444; 153728</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>150819; 215218</t>
+          <t>170832; 230548</t>
         </is>
       </c>
     </row>
